--- a/artfynd/A 32245-2021 artfynd.xlsx
+++ b/artfynd/A 32245-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32245-2021 artfynd.xlsx
+++ b/artfynd/A 32245-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73968437</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100679</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483724.0869650138</v>
+        <v>483724</v>
       </c>
       <c r="R2" t="n">
-        <v>6390544.650286106</v>
+        <v>6390545</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1986-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 32245-2021 artfynd.xlsx
+++ b/artfynd/A 32245-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968437</v>
       </c>
       <c r="B2" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32245-2021 artfynd.xlsx
+++ b/artfynd/A 32245-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968437</v>
       </c>
       <c r="B2" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32245-2021 artfynd.xlsx
+++ b/artfynd/A 32245-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968437</v>
       </c>
       <c r="B2" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32245-2021 artfynd.xlsx
+++ b/artfynd/A 32245-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968437</v>
       </c>
       <c r="B2" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32245-2021 artfynd.xlsx
+++ b/artfynd/A 32245-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968437</v>
       </c>
       <c r="B2" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32245-2021 artfynd.xlsx
+++ b/artfynd/A 32245-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968437</v>
       </c>
       <c r="B2" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32245-2021 artfynd.xlsx
+++ b/artfynd/A 32245-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968437</v>
       </c>
       <c r="B2" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32245-2021 artfynd.xlsx
+++ b/artfynd/A 32245-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968437</v>
       </c>
       <c r="B2" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32245-2021 artfynd.xlsx
+++ b/artfynd/A 32245-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968437</v>
       </c>
       <c r="B2" t="n">
-        <v>100745</v>
+        <v>100753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32245-2021 artfynd.xlsx
+++ b/artfynd/A 32245-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73968437</v>
       </c>
       <c r="B2" t="n">
-        <v>100753</v>
+        <v>100763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32245-2021 artfynd.xlsx
+++ b/artfynd/A 32245-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,62 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73968437</v>
+        <v>127887580</v>
       </c>
       <c r="B2" t="n">
-        <v>100763</v>
+        <v>56845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>100053</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>L8 Muggebo 300 m NV, Sm</t>
+          <t>Smultronstigen 21, 571 38 Nässjö, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483724</v>
+        <v>483618</v>
       </c>
       <c r="R2" t="n">
-        <v>6390545</v>
+        <v>6390462</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1980-01-01</t>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1986-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 6E8h 2906. SOM: Actaea spicata. LEG: Barbro Svensson,  Brita Ekenfall</t>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,24 +780,477 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lund</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Via Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>52909815</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hultet, Nässjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>483714</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6390467</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2015-04-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2015-04-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lennart Öhmark</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lennart Öhmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>52909844</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hultet, Nässjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>483714</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6390467</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2015-04-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2015-04-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lennart Öhmark</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lennart Öhmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>74119143</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101896</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>L8 Muggebo 300 m NV, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>483724</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6390545</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1986-12-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6E8h 2906. SOM: Chrysosplenium alternifolium. LEG: Barbro Svensson, Brita Ekenfall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Fukt. äng</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>73968437</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101227</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>L8 Muggebo 300 m NV, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>483724</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6390545</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1980-01-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1986-12-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 6E8h 2906. SOM: Actaea spicata. LEG: Barbro Svensson,  Brita Ekenfall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>
